--- a/Result/profitability/6771.xlsx
+++ b/Result/profitability/6771.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,6 +3605,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6771</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>146</v>
+      </c>
+      <c r="D26" t="n">
+        <v>78</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68</v>
+      </c>
+      <c r="F26" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>26.93%</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>32</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8887499999999999</v>
+      </c>
+      <c r="N26" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09000000000000008</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.1304347826086958</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.00999999999999801</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.0002135839384878047</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.1235955056179775</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.3699999999999974</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-0.007842306061890625</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
